--- a/data/trans_camb/P1409-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1409-Edad-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>1,3</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,43</t>
+          <t>-1,53; 3,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 8,57</t>
+          <t>-0,73; 8,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 5,12</t>
+          <t>-0,33; 4,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,1</t>
+          <t>-2,92; 2,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 3,68</t>
+          <t>-0,25; 3,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 4,65</t>
+          <t>-1,14; 3,87</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-24,98%</t>
+          <t>-17,4%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,0%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 183,62</t>
+          <t>-38,5; 170,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 418,22</t>
+          <t>-26,39; 405,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 268,01</t>
+          <t>-10,91; 263,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-83,06; 132,96</t>
+          <t>-77,42; 156,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 164,43</t>
+          <t>-8,0; 154,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,36; 193,25</t>
+          <t>-35,33; 170,62</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,56</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,42</t>
+          <t>0,53</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,53</t>
+          <t>2,35</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,48</t>
+          <t>-0,95; 2,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 8,31</t>
+          <t>1,39; 7,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 2,35</t>
+          <t>-1,96; 2,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 47,63</t>
+          <t>-1,74; 2,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,83</t>
+          <t>-0,84; 1,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 30,4</t>
+          <t>0,49; 4,13</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>228,73%</t>
+          <t>207,13%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>371,39%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>345,81%</t>
+          <t>85,41%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 196,67</t>
+          <t>-37,48; 149,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71,86; 545,15</t>
+          <t>44,93; 500,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,98; 89,73</t>
+          <t>-43,39; 93,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 1969,7</t>
+          <t>-37,4; 120,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 82,33</t>
+          <t>-25,11; 86,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,76; 1438,64</t>
+          <t>8,48; 182,56</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>2,57</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,55</t>
+          <t>2,35</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,13</t>
+          <t>-0,86; 2,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,17</t>
+          <t>0,8; 4,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,9</t>
+          <t>-0,7; 2,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,41</t>
+          <t>0,22; 4,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,0</t>
+          <t>-0,37; 2,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,95</t>
+          <t>1,0; 3,54</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>205,45%</t>
+          <t>194,69%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101,02%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>136,93%</t>
+          <t>126,0%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,54; 273,02</t>
+          <t>-47,14; 270,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,67; 603,5</t>
+          <t>27,21; 578,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,28; 205,88</t>
+          <t>-23,89; 186,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,42; 294,84</t>
+          <t>-2,33; 244,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 144,76</t>
+          <t>-18,9; 147,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,57; 292,6</t>
+          <t>41,79; 271,11</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>2,0</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,71</t>
+          <t>3,94</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>3,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 1,54</t>
+          <t>-1,3; 1,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,94</t>
+          <t>0,17; 3,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,48</t>
+          <t>-0,25; 3,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,49</t>
+          <t>2,03; 5,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,12</t>
+          <t>-0,26; 1,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,6</t>
+          <t>1,81; 4,13</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>111,98%</t>
+          <t>193,18%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>216,4%</t>
+          <t>229,9%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>164,2%</t>
+          <t>218,44%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-70,4; 342,27</t>
+          <t>-75,54; 325,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 716,43</t>
+          <t>-12,23; 863,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 391,46</t>
+          <t>-13,52; 361,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56,57; 664,7</t>
+          <t>50,47; 629,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 247,41</t>
+          <t>-19,71; 218,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,01; 419,88</t>
+          <t>75,07; 464,32</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,67</t>
+          <t>1,66</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,53</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,52</t>
+          <t>-0,48; 3,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,37</t>
+          <t>-0,09; 3,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,66</t>
+          <t>-1,76; 3,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,5</t>
+          <t>-0,56; 3,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,81</t>
+          <t>-0,48; 2,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,82</t>
+          <t>0,11; 2,71</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>124,12%</t>
+          <t>118,78%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>72,83%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,98; 795,78</t>
+          <t>-38,59; 565,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,95; 689,49</t>
+          <t>-16,24; 678,78</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,17; 203,51</t>
+          <t>-41,51; 197,6</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 192,97</t>
+          <t>-14,36; 241,12</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 203,31</t>
+          <t>-19,76; 184,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 199,69</t>
+          <t>0,08; 198,92</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,45</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>1,0</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 0,71</t>
+          <t>-4,78; 0,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 1,97</t>
+          <t>-3,02; 1,86</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 3,99</t>
+          <t>-1,17; 3,87</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,69</t>
+          <t>-0,01; 4,33</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,79</t>
+          <t>-1,87; 1,9</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,87</t>
+          <t>-0,78; 2,66</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-9,12%</t>
+          <t>-13,51%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>34,6%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-84,09; 57,32</t>
+          <t>-87,12; 63,28</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-64,79; 128,26</t>
+          <t>-61,15; 130,01</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-26,61; 289,09</t>
+          <t>-34,57; 340,92</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-63,76; 149,05</t>
+          <t>-5,92; 335,17</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-50,44; 92,48</t>
+          <t>-47,85; 98,34</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-55,03; 88,01</t>
+          <t>-20,76; 154,78</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3,24</t>
+          <t>3,23</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>1,98</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 6,14</t>
+          <t>-0,57; 6,29</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 2,69</t>
+          <t>-3,38; 2,5</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,85</t>
+          <t>-0,94; 4,94</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,81</t>
+          <t>0,7; 5,73</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 4,59</t>
+          <t>0,01; 4,57</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,74</t>
+          <t>-0,03; 3,6</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>105,69%</t>
+          <t>105,35%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,26%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 386,63</t>
+          <t>-21,87; 354,66</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-58,84; 208,82</t>
+          <t>-61,47; 173,76</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-34,35; 266,76</t>
+          <t>-26,15; 289,37</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6,75; 321,62</t>
+          <t>9,28; 335,53</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 215,54</t>
+          <t>-2,94; 235,26</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 187,48</t>
+          <t>-5,23; 179,32</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3,57</t>
+          <t>2,06</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,7</t>
+          <t>2,01</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,35</t>
+          <t>-0,11; 1,35</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,84</t>
+          <t>1,09; 2,93</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,15</t>
+          <t>0,46; 2,14</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,35; 10,75</t>
+          <t>1,21; 2,89</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,54</t>
+          <t>0,37; 1,51</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,59</t>
+          <t>1,38; 2,6</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>101,71%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>131,84%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>116,63%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 83,14</t>
+          <t>-4,99; 83,63</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>31,05; 170,16</t>
+          <t>48,32; 179,61</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9,84; 90,63</t>
+          <t>14,74; 94,22</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>47,02; 397,25</t>
+          <t>36,71; 127,86</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>15,43; 74,24</t>
+          <t>14,04; 73,66</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>64,6; 302,03</t>
+          <t>53,7; 126,17</t>
         </is>
       </c>
     </row>
